--- a/data/file_generation/reference/data_107/H店_揽收明细_res.xlsx
+++ b/data/file_generation/reference/data_107/H店_揽收明细_res.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chenyanbing/files/26/0206/data_107/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chenyanbing/files/26/0205/ai办公标注/output/data_107/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63917BF6-84BB-0D4F-9DF0-DA4449D99316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B5BBC35-43A0-3D48-8161-D292CF4A1424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1080" yWindow="500" windowWidth="34760" windowHeight="21900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="105">
   <si>
     <t>运单编号</t>
   </si>
@@ -62,9 +62,6 @@
     <t>客户F</t>
   </si>
   <si>
-    <t>2025-10-17 18:35:30</t>
-  </si>
-  <si>
     <t>贵州省</t>
   </si>
   <si>
@@ -77,42 +74,27 @@
     <t>L1MFLKZEVY4G</t>
   </si>
   <si>
-    <t>2025-10-17 18:35:33</t>
-  </si>
-  <si>
     <t>吉林省</t>
   </si>
   <si>
     <t>ODJBZNFU5SEN</t>
   </si>
   <si>
-    <t>2025-10-17 18:35:34</t>
-  </si>
-  <si>
     <t>四川省</t>
   </si>
   <si>
     <t>NZ1QMSLDM3HL</t>
   </si>
   <si>
-    <t>2025-10-26 15:02:48</t>
-  </si>
-  <si>
     <t>CRZQX5G6HXGU</t>
   </si>
   <si>
-    <t>2025-10-26 15:02:49</t>
-  </si>
-  <si>
     <t>云南省</t>
   </si>
   <si>
     <t>898RKDLJF0JR</t>
   </si>
   <si>
-    <t>2025-10-26 15:02:52</t>
-  </si>
-  <si>
     <t>广西壮族自治区</t>
   </si>
   <si>
@@ -122,72 +104,42 @@
     <t>FQURTH6R1FBS</t>
   </si>
   <si>
-    <t>2025-10-27 18:59:41</t>
-  </si>
-  <si>
     <t>1T6MBXI0OQC0</t>
   </si>
   <si>
-    <t>2025-10-27 18:59:42</t>
-  </si>
-  <si>
     <t>FC2KYOIH7KA8</t>
   </si>
   <si>
-    <t>2025-10-28 12:53:09</t>
-  </si>
-  <si>
     <t>NP32HTD26JW0</t>
   </si>
   <si>
-    <t>2025-10-28 12:53:10</t>
-  </si>
-  <si>
     <t>EOIL8OEZDMFX</t>
   </si>
   <si>
-    <t>2025-10-28 12:53:15</t>
-  </si>
-  <si>
     <t>R5G6A79R74H9</t>
   </si>
   <si>
-    <t>2025-10-28 12:53:18</t>
-  </si>
-  <si>
     <t>辽宁省</t>
   </si>
   <si>
     <t>R0RX5XAQPNYJ</t>
   </si>
   <si>
-    <t>2025-10-29 13:02:58</t>
-  </si>
-  <si>
     <t>NFCEB1IP7W9Y</t>
   </si>
   <si>
     <t>7F22O4I51G7B</t>
   </si>
   <si>
-    <t>2025-10-29 13:03:00</t>
-  </si>
-  <si>
     <t>16IU1UFEZG1I</t>
   </si>
   <si>
-    <t>2025-10-29 13:03:01</t>
-  </si>
-  <si>
     <t>江苏省</t>
   </si>
   <si>
     <t>0L1ZQJJZVG4F</t>
   </si>
   <si>
-    <t>2025-10-29 13:03:02</t>
-  </si>
-  <si>
     <t>黑龙江省</t>
   </si>
   <si>
@@ -197,81 +149,42 @@
     <t>5XBPTT9Z6PXH</t>
   </si>
   <si>
-    <t>2025-10-29 13:03:03</t>
-  </si>
-  <si>
     <t>V5FMM097VSPU</t>
   </si>
   <si>
-    <t>2025-10-29 13:03:04</t>
-  </si>
-  <si>
     <t>3Z9XR25QWV0C</t>
   </si>
   <si>
-    <t>2025-10-29 13:03:05</t>
-  </si>
-  <si>
     <t>4JXPWGC84O87</t>
   </si>
   <si>
-    <t>2025-10-29 13:03:06</t>
-  </si>
-  <si>
     <t>M5GP4W5H7OCM</t>
   </si>
   <si>
-    <t>2025-10-30 12:55:42</t>
-  </si>
-  <si>
     <t>SSL2JB8VNY5J</t>
   </si>
   <si>
-    <t>2025-10-30 12:56:08</t>
-  </si>
-  <si>
     <t>ZABXAIRWSPFX</t>
   </si>
   <si>
-    <t>2025-10-31 12:55:24</t>
-  </si>
-  <si>
     <t>POZ31QTQ5V7H</t>
   </si>
   <si>
-    <t>2025-10-31 12:55:25</t>
-  </si>
-  <si>
     <t>T1LLLU68IIQ2</t>
   </si>
   <si>
-    <t>2025-10-31 12:55:26</t>
-  </si>
-  <si>
     <t>TU0YVXQPKAGQ</t>
   </si>
   <si>
-    <t>2025-10-31 12:55:44</t>
-  </si>
-  <si>
     <t>43LVPCQ8V1N2</t>
   </si>
   <si>
-    <t>2025-10-31 12:55:50</t>
-  </si>
-  <si>
     <t>PWCCRZ31UKYE</t>
   </si>
   <si>
-    <t>2025-10-31 12:56:18</t>
-  </si>
-  <si>
     <t>P11IUDITBSYT</t>
   </si>
   <si>
-    <t>2025-10-29 13:02:59</t>
-  </si>
-  <si>
     <t>北京</t>
   </si>
   <si>
@@ -281,33 +194,18 @@
     <t>PP4OFDHGN8ZH</t>
   </si>
   <si>
-    <t>2025-10-28 12:53:16</t>
-  </si>
-  <si>
     <t>0BS5O5SKK6RY</t>
   </si>
   <si>
-    <t>2025-10-31 12:55:53</t>
-  </si>
-  <si>
     <t>R0UW9UKAWWRP</t>
   </si>
   <si>
-    <t>2025-10-30 12:55:34</t>
-  </si>
-  <si>
     <t>WO38SL134R8Z</t>
   </si>
   <si>
-    <t>2025-10-30 12:56:04</t>
-  </si>
-  <si>
     <t>BR3MVVB8U964</t>
   </si>
   <si>
-    <t>2025-10-30 12:55:41</t>
-  </si>
-  <si>
     <t>5L9X33B03YD8</t>
   </si>
   <si>
@@ -320,39 +218,21 @@
     <t>L1XD76FBGDYT</t>
   </si>
   <si>
-    <t>2025-10-17 18:35:35</t>
-  </si>
-  <si>
     <t>286O2PDMN3R3</t>
   </si>
   <si>
-    <t>2025-10-30 12:56:03</t>
-  </si>
-  <si>
     <t>NKZBQ6X77J52</t>
   </si>
   <si>
-    <t>2025-10-30 12:56:07</t>
-  </si>
-  <si>
     <t>23UBJIWPVJ9C</t>
   </si>
   <si>
-    <t>2025-10-31 12:55:47</t>
-  </si>
-  <si>
     <t>NV9H5ZJXCI21</t>
   </si>
   <si>
-    <t>2025-10-29 13:03:08</t>
-  </si>
-  <si>
     <t>NU94CQSD49X7</t>
   </si>
   <si>
-    <t>2025-10-27 19:20:22</t>
-  </si>
-  <si>
     <t>63TSSEM4KDZ0</t>
   </si>
   <si>
@@ -362,9 +242,6 @@
     <t>JDMNJC3LQF80</t>
   </si>
   <si>
-    <t>2025-10-30 12:55:30</t>
-  </si>
-  <si>
     <t>浙江省</t>
   </si>
   <si>
@@ -374,156 +251,87 @@
     <t>W96N87YTPL31</t>
   </si>
   <si>
-    <t>2025-10-29 13:03:07</t>
-  </si>
-  <si>
     <t>BSPQ99346WL1</t>
   </si>
   <si>
-    <t>2025-10-28 12:53:19</t>
-  </si>
-  <si>
     <t>DX96ANU7PL9J</t>
   </si>
   <si>
-    <t>2025-10-30 12:55:48</t>
-  </si>
-  <si>
     <t>Z2WXZ3IBAUY8</t>
   </si>
   <si>
-    <t>2025-10-26 15:02:47</t>
-  </si>
-  <si>
     <t>17LZ04T0OJR8</t>
   </si>
   <si>
-    <t>2025-10-31 12:55:59</t>
-  </si>
-  <si>
     <t>PX87A6FPG1QT</t>
   </si>
   <si>
-    <t>2025-10-17 18:35:44</t>
-  </si>
-  <si>
     <t>0OP4DR44SHJH</t>
   </si>
   <si>
-    <t>2025-10-26 15:02:44</t>
-  </si>
-  <si>
     <t>青海省</t>
   </si>
   <si>
     <t>DHYNZC7VQ6JO</t>
   </si>
   <si>
-    <t>2025-10-31 12:57:37</t>
-  </si>
-  <si>
     <t>42D8CJQ8VB1B</t>
   </si>
   <si>
-    <t>2025-10-30 12:55:46</t>
-  </si>
-  <si>
     <t>008KPPS3IWC9</t>
   </si>
   <si>
-    <t>2025-10-31 12:56:48</t>
-  </si>
-  <si>
     <t>68SOV43WGAW7</t>
   </si>
   <si>
-    <t>2025-10-31 12:56:49</t>
-  </si>
-  <si>
     <t>GY15RQUSDMLI</t>
   </si>
   <si>
-    <t>2025-10-31 12:57:10</t>
-  </si>
-  <si>
     <t>YUDN6XBH9WTD</t>
   </si>
   <si>
     <t>RCWX0I3C2OW6</t>
   </si>
   <si>
-    <t>2025-10-17 18:35:28</t>
-  </si>
-  <si>
     <t>NIZ7S2RWCF48</t>
   </si>
   <si>
-    <t>2025-10-31 12:56:47</t>
-  </si>
-  <si>
     <t>XZBJVMZ0J5T1</t>
   </si>
   <si>
     <t>3N0KIMYLMUNY</t>
   </si>
   <si>
-    <t>2025-10-31 12:57:11</t>
-  </si>
-  <si>
     <t>4FR8N5QVJPKA</t>
   </si>
   <si>
-    <t>2025-10-17 18:35:42</t>
-  </si>
-  <si>
     <t>VS2NLSNN71XR</t>
   </si>
   <si>
-    <t>2025-10-29 13:02:55</t>
-  </si>
-  <si>
     <t>581GEIXP27LT</t>
   </si>
   <si>
-    <t>2025-10-31 12:56:19</t>
-  </si>
-  <si>
     <t>5YQR6UFML52J</t>
   </si>
   <si>
-    <t>2025-10-31 12:56:21</t>
-  </si>
-  <si>
     <t>EOBL0VPT7I1U</t>
   </si>
   <si>
     <t>JZIL4XWDVFFX</t>
   </si>
   <si>
-    <t>2025-10-31 12:56:22</t>
-  </si>
-  <si>
     <t>AAMKISMPTJ96</t>
   </si>
   <si>
-    <t>2025-10-26 15:02:45</t>
-  </si>
-  <si>
     <t>8APD6PYDBROL</t>
   </si>
   <si>
-    <t>2025-10-17 11:09:44</t>
-  </si>
-  <si>
     <t>JRB0N23C90Z3</t>
   </si>
   <si>
     <t>E1CDET66PFSP</t>
   </si>
   <si>
-    <t>2025-10-26 15:02:46</t>
-  </si>
-  <si>
     <t>广东省</t>
   </si>
   <si>
@@ -533,19 +341,13 @@
     <t>9EWN034P9RRX</t>
   </si>
   <si>
-    <t>2025-10-30 12:55:29</t>
-  </si>
-  <si>
     <t>3VIKE6ARW1T4</t>
   </si>
   <si>
-    <t>2025-10-27 19:20:26</t>
-  </si>
-  <si>
     <t>IU82U8SC2E5P</t>
   </si>
   <si>
-    <t>2025-10-27 19:20:24</t>
+    <t>2025年10月</t>
   </si>
 </sst>
 </file>
@@ -946,10 +748,10 @@
         <v>8</v>
       </c>
       <c r="C2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D2" t="s">
         <v>9</v>
-      </c>
-      <c r="D2" t="s">
-        <v>10</v>
       </c>
       <c r="E2">
         <v>0.46</v>
@@ -958,10 +760,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="G2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="I2">
         <f>ROUND(272.2-81*1.8,2)</f>
@@ -970,16 +772,16 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D3" t="s">
         <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" t="s">
-        <v>15</v>
       </c>
       <c r="E3">
         <v>0.46</v>
@@ -990,16 +792,16 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>104</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E4">
         <v>0.67</v>
@@ -1010,16 +812,16 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E5">
         <v>0.76</v>
@@ -1030,16 +832,16 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
         <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>104</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E6">
         <v>0.64</v>
@@ -1050,16 +852,16 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
         <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E7">
         <v>0.63</v>
@@ -1070,16 +872,16 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
         <v>8</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="D8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E8">
         <v>0.63</v>
@@ -1090,16 +892,16 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B9" t="s">
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>104</v>
       </c>
       <c r="D9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E9">
         <v>0.5</v>
@@ -1110,16 +912,16 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s">
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>31</v>
+        <v>104</v>
       </c>
       <c r="D10" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E10">
         <v>0.5</v>
@@ -1130,16 +932,16 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B11" t="s">
         <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>104</v>
       </c>
       <c r="D11" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E11">
         <v>0.46</v>
@@ -1150,16 +952,16 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B12" t="s">
         <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>35</v>
+        <v>104</v>
       </c>
       <c r="D12" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E12">
         <v>0.52</v>
@@ -1170,16 +972,16 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="B13" t="s">
         <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>104</v>
       </c>
       <c r="D13" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E13">
         <v>0.56999999999999995</v>
@@ -1190,16 +992,16 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="B14" t="s">
         <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>39</v>
+        <v>104</v>
       </c>
       <c r="D14" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="E14">
         <v>0.59</v>
@@ -1210,16 +1012,16 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="B15" t="s">
         <v>8</v>
       </c>
       <c r="C15" t="s">
-        <v>42</v>
+        <v>104</v>
       </c>
       <c r="D15" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E15">
         <v>0.54</v>
@@ -1230,16 +1032,16 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="B16" t="s">
         <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>42</v>
+        <v>104</v>
       </c>
       <c r="D16" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E16">
         <v>0.65</v>
@@ -1250,16 +1052,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="B17" t="s">
         <v>8</v>
       </c>
       <c r="C17" t="s">
-        <v>45</v>
+        <v>104</v>
       </c>
       <c r="D17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E17">
         <v>0.37</v>
@@ -1270,16 +1072,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s">
         <v>8</v>
       </c>
       <c r="C18" t="s">
-        <v>47</v>
+        <v>104</v>
       </c>
       <c r="D18" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="E18">
         <v>0.62</v>
@@ -1290,16 +1092,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s">
         <v>8</v>
       </c>
       <c r="C19" t="s">
-        <v>50</v>
+        <v>104</v>
       </c>
       <c r="D19" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="E19">
         <v>0.63</v>
@@ -1310,16 +1112,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="B20" t="s">
         <v>8</v>
       </c>
       <c r="C20" t="s">
-        <v>50</v>
+        <v>104</v>
       </c>
       <c r="D20" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="E20">
         <v>0.71</v>
@@ -1330,16 +1132,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="B21" t="s">
         <v>8</v>
       </c>
       <c r="C21" t="s">
-        <v>54</v>
+        <v>104</v>
       </c>
       <c r="D21" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="E21">
         <v>0.61</v>
@@ -1350,16 +1152,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="B22" t="s">
         <v>8</v>
       </c>
       <c r="C22" t="s">
-        <v>56</v>
+        <v>104</v>
       </c>
       <c r="D22" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E22">
         <v>0.9</v>
@@ -1370,16 +1172,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="B23" t="s">
         <v>8</v>
       </c>
       <c r="C23" t="s">
-        <v>58</v>
+        <v>104</v>
       </c>
       <c r="D23" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="E23">
         <v>0.64</v>
@@ -1390,16 +1192,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="B24" t="s">
         <v>8</v>
       </c>
       <c r="C24" t="s">
-        <v>60</v>
+        <v>104</v>
       </c>
       <c r="D24" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E24">
         <v>0.66</v>
@@ -1410,16 +1212,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="B25" t="s">
         <v>8</v>
       </c>
       <c r="C25" t="s">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="D25" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E25">
         <v>0.63</v>
@@ -1430,16 +1232,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="B26" t="s">
         <v>8</v>
       </c>
       <c r="C26" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="D26" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="E26">
         <v>0.61</v>
@@ -1450,16 +1252,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="B27" t="s">
         <v>8</v>
       </c>
       <c r="C27" t="s">
-        <v>66</v>
+        <v>104</v>
       </c>
       <c r="D27" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E27">
         <v>0.61</v>
@@ -1470,16 +1272,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="B28" t="s">
         <v>8</v>
       </c>
       <c r="C28" t="s">
-        <v>68</v>
+        <v>104</v>
       </c>
       <c r="D28" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="E28">
         <v>0.62</v>
@@ -1490,16 +1292,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="B29" t="s">
         <v>8</v>
       </c>
       <c r="C29" t="s">
-        <v>70</v>
+        <v>104</v>
       </c>
       <c r="D29" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E29">
         <v>0.59</v>
@@ -1510,16 +1312,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="B30" t="s">
         <v>8</v>
       </c>
       <c r="C30" t="s">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="D30" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="E30">
         <v>0.63</v>
@@ -1530,16 +1332,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="B31" t="s">
         <v>8</v>
       </c>
       <c r="C31" t="s">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="D31" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="E31">
         <v>0.61</v>
@@ -1550,16 +1352,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="B32" t="s">
         <v>8</v>
       </c>
       <c r="C32" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="D32" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="E32">
         <v>0.6</v>
@@ -1570,16 +1372,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="B33" t="s">
         <v>8</v>
       </c>
       <c r="C33" t="s">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="D33" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="E33">
         <v>0.56000000000000005</v>
@@ -1590,16 +1392,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="B34" t="s">
         <v>8</v>
       </c>
       <c r="C34" t="s">
-        <v>39</v>
+        <v>104</v>
       </c>
       <c r="D34" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="E34">
         <v>0.56999999999999995</v>
@@ -1610,16 +1412,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="B35" t="s">
         <v>8</v>
       </c>
       <c r="C35" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="D35" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="E35">
         <v>0.57999999999999996</v>
@@ -1630,16 +1432,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="B36" t="s">
         <v>8</v>
       </c>
       <c r="C36" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="D36" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="E36">
         <v>0.61</v>
@@ -1650,16 +1452,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="B37" t="s">
         <v>8</v>
       </c>
       <c r="C37" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="D37" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="E37">
         <v>0.62</v>
@@ -1670,16 +1472,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>87</v>
+        <v>55</v>
       </c>
       <c r="B38" t="s">
         <v>8</v>
       </c>
       <c r="C38" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="D38" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="E38">
         <v>0.62</v>
@@ -1690,16 +1492,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
-        <v>89</v>
+        <v>56</v>
       </c>
       <c r="B39" t="s">
         <v>8</v>
       </c>
       <c r="C39" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="D39" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="E39">
         <v>0.63</v>
@@ -1710,16 +1512,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>91</v>
+        <v>57</v>
       </c>
       <c r="B40" t="s">
         <v>8</v>
       </c>
       <c r="C40" t="s">
-        <v>70</v>
+        <v>104</v>
       </c>
       <c r="D40" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="E40">
         <v>0.63</v>
@@ -1730,16 +1532,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="B41" t="s">
         <v>8</v>
       </c>
       <c r="C41" t="s">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="D41" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="E41">
         <v>0.63</v>
@@ -1750,16 +1552,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>93</v>
+        <v>59</v>
       </c>
       <c r="B42" t="s">
         <v>8</v>
       </c>
       <c r="C42" t="s">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="D42" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="E42">
         <v>0.64</v>
@@ -1770,16 +1572,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="B43" t="s">
         <v>8</v>
       </c>
       <c r="C43" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="D43" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="E43">
         <v>0.65</v>
@@ -1790,16 +1592,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" t="s">
-        <v>96</v>
+        <v>61</v>
       </c>
       <c r="B44" t="s">
         <v>8</v>
       </c>
       <c r="C44" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="D44" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="E44">
         <v>0.66</v>
@@ -1810,16 +1612,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" t="s">
-        <v>98</v>
+        <v>62</v>
       </c>
       <c r="B45" t="s">
         <v>8</v>
       </c>
       <c r="C45" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D45" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="E45">
         <v>0.66</v>
@@ -1830,16 +1632,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" t="s">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="B46" t="s">
         <v>8</v>
       </c>
       <c r="C46" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D46" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="E46">
         <v>0.76</v>
@@ -1850,16 +1652,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" t="s">
-        <v>102</v>
+        <v>64</v>
       </c>
       <c r="B47" t="s">
         <v>8</v>
       </c>
       <c r="C47" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D47" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E47">
         <v>1.87</v>
@@ -1870,16 +1672,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" t="s">
-        <v>104</v>
+        <v>65</v>
       </c>
       <c r="B48" t="s">
         <v>8</v>
       </c>
       <c r="C48" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D48" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="E48">
         <v>1.87</v>
@@ -1890,16 +1692,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" t="s">
-        <v>106</v>
+        <v>66</v>
       </c>
       <c r="B49" t="s">
         <v>8</v>
       </c>
       <c r="C49" t="s">
-        <v>60</v>
+        <v>104</v>
       </c>
       <c r="D49" t="s">
-        <v>107</v>
+        <v>67</v>
       </c>
       <c r="E49">
         <v>1.88</v>
@@ -1910,16 +1712,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" t="s">
-        <v>108</v>
+        <v>68</v>
       </c>
       <c r="B50" t="s">
         <v>8</v>
       </c>
       <c r="C50" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D50" t="s">
-        <v>110</v>
+        <v>69</v>
       </c>
       <c r="E50">
         <v>1.88</v>
@@ -1930,16 +1732,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" t="s">
-        <v>111</v>
+        <v>70</v>
       </c>
       <c r="B51" t="s">
         <v>8</v>
       </c>
       <c r="C51" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D51" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="E51">
         <v>1.89</v>
@@ -1950,16 +1752,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" t="s">
-        <v>112</v>
+        <v>71</v>
       </c>
       <c r="B52" t="s">
         <v>8</v>
       </c>
       <c r="C52" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="D52" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="E52">
         <v>1.9</v>
@@ -1970,16 +1772,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" t="s">
-        <v>114</v>
+        <v>72</v>
       </c>
       <c r="B53" t="s">
         <v>8</v>
       </c>
       <c r="C53" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="D53" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E53">
         <v>1.91</v>
@@ -1990,16 +1792,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" t="s">
-        <v>116</v>
+        <v>73</v>
       </c>
       <c r="B54" t="s">
         <v>8</v>
       </c>
       <c r="C54" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="D54" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="E54">
         <v>1.91</v>
@@ -2010,16 +1812,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" t="s">
-        <v>118</v>
+        <v>74</v>
       </c>
       <c r="B55" t="s">
         <v>8</v>
       </c>
       <c r="C55" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="D55" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E55">
         <v>1.92</v>
@@ -2030,16 +1832,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" t="s">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="B56" t="s">
         <v>8</v>
       </c>
       <c r="C56" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="D56" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="E56">
         <v>2.17</v>
@@ -2050,16 +1852,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" t="s">
-        <v>122</v>
+        <v>76</v>
       </c>
       <c r="B57" t="s">
         <v>8</v>
       </c>
       <c r="C57" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="D57" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E57">
         <v>2.31</v>
@@ -2070,16 +1872,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" t="s">
-        <v>124</v>
+        <v>77</v>
       </c>
       <c r="B58" t="s">
         <v>8</v>
       </c>
       <c r="C58" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="D58" t="s">
-        <v>126</v>
+        <v>78</v>
       </c>
       <c r="E58">
         <v>2.33</v>
@@ -2090,16 +1892,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" t="s">
-        <v>127</v>
+        <v>79</v>
       </c>
       <c r="B59" t="s">
         <v>8</v>
       </c>
       <c r="C59" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="D59" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E59">
         <v>2.4500000000000002</v>
@@ -2110,16 +1912,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" t="s">
-        <v>129</v>
+        <v>80</v>
       </c>
       <c r="B60" t="s">
         <v>8</v>
       </c>
       <c r="C60" t="s">
-        <v>130</v>
+        <v>104</v>
       </c>
       <c r="D60" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E60">
         <v>2.48</v>
@@ -2130,16 +1932,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" t="s">
-        <v>131</v>
+        <v>81</v>
       </c>
       <c r="B61" t="s">
         <v>8</v>
       </c>
       <c r="C61" t="s">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="D61" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E61">
         <v>2.5099999999999998</v>
@@ -2150,16 +1952,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" t="s">
-        <v>133</v>
+        <v>82</v>
       </c>
       <c r="B62" t="s">
         <v>8</v>
       </c>
       <c r="C62" t="s">
-        <v>134</v>
+        <v>104</v>
       </c>
       <c r="D62" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E62">
         <v>2.5099999999999998</v>
@@ -2170,16 +1972,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" t="s">
-        <v>135</v>
+        <v>83</v>
       </c>
       <c r="B63" t="s">
         <v>8</v>
       </c>
       <c r="C63" t="s">
-        <v>136</v>
+        <v>104</v>
       </c>
       <c r="D63" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E63">
         <v>2.5099999999999998</v>
@@ -2190,16 +1992,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" t="s">
-        <v>137</v>
+        <v>84</v>
       </c>
       <c r="B64" t="s">
         <v>8</v>
       </c>
       <c r="C64" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="D64" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E64">
         <v>2.5099999999999998</v>
@@ -2210,16 +2012,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" t="s">
-        <v>138</v>
+        <v>85</v>
       </c>
       <c r="B65" t="s">
         <v>8</v>
       </c>
       <c r="C65" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="D65" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E65">
         <v>2.5299999999999998</v>
@@ -2230,16 +2032,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" t="s">
-        <v>140</v>
+        <v>86</v>
       </c>
       <c r="B66" t="s">
         <v>8</v>
       </c>
       <c r="C66" t="s">
-        <v>141</v>
+        <v>104</v>
       </c>
       <c r="D66" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E66">
         <v>2.5299999999999998</v>
@@ -2250,16 +2052,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" t="s">
-        <v>142</v>
+        <v>87</v>
       </c>
       <c r="B67" t="s">
         <v>8</v>
       </c>
       <c r="C67" t="s">
-        <v>136</v>
+        <v>104</v>
       </c>
       <c r="D67" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E67">
         <v>2.5299999999999998</v>
@@ -2270,16 +2072,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" t="s">
-        <v>143</v>
+        <v>88</v>
       </c>
       <c r="B68" t="s">
         <v>8</v>
       </c>
       <c r="C68" t="s">
-        <v>144</v>
+        <v>104</v>
       </c>
       <c r="D68" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E68">
         <v>2.5299999999999998</v>
@@ -2290,16 +2092,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" t="s">
-        <v>145</v>
+        <v>89</v>
       </c>
       <c r="B69" t="s">
         <v>8</v>
       </c>
       <c r="C69" t="s">
-        <v>146</v>
+        <v>104</v>
       </c>
       <c r="D69" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E69">
         <v>2.54</v>
@@ -2310,16 +2112,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" t="s">
-        <v>147</v>
+        <v>90</v>
       </c>
       <c r="B70" t="s">
         <v>8</v>
       </c>
       <c r="C70" t="s">
-        <v>148</v>
+        <v>104</v>
       </c>
       <c r="D70" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E70">
         <v>2.5499999999999998</v>
@@ -2330,16 +2132,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" t="s">
-        <v>149</v>
+        <v>91</v>
       </c>
       <c r="B71" t="s">
         <v>8</v>
       </c>
       <c r="C71" t="s">
-        <v>150</v>
+        <v>104</v>
       </c>
       <c r="D71" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="E71">
         <v>2.78</v>
@@ -2350,16 +2152,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" t="s">
-        <v>151</v>
+        <v>92</v>
       </c>
       <c r="B72" t="s">
         <v>8</v>
       </c>
       <c r="C72" t="s">
-        <v>152</v>
+        <v>104</v>
       </c>
       <c r="D72" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="E72">
         <v>2.78</v>
@@ -2370,16 +2172,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" t="s">
-        <v>153</v>
+        <v>93</v>
       </c>
       <c r="B73" t="s">
         <v>8</v>
       </c>
       <c r="C73" t="s">
-        <v>152</v>
+        <v>104</v>
       </c>
       <c r="D73" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="E73">
         <v>2.78</v>
@@ -2390,16 +2192,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" t="s">
-        <v>154</v>
+        <v>94</v>
       </c>
       <c r="B74" t="s">
         <v>8</v>
       </c>
       <c r="C74" t="s">
-        <v>155</v>
+        <v>104</v>
       </c>
       <c r="D74" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="E74">
         <v>2.78</v>
@@ -2410,16 +2212,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" t="s">
-        <v>156</v>
+        <v>95</v>
       </c>
       <c r="B75" t="s">
         <v>8</v>
       </c>
       <c r="C75" t="s">
-        <v>157</v>
+        <v>104</v>
       </c>
       <c r="D75" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="E75">
         <v>2.8</v>
@@ -2430,16 +2232,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" t="s">
-        <v>158</v>
+        <v>96</v>
       </c>
       <c r="B76" t="s">
         <v>8</v>
       </c>
       <c r="C76" t="s">
-        <v>159</v>
+        <v>104</v>
       </c>
       <c r="D76" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E76">
         <v>2.81</v>
@@ -2450,16 +2252,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" t="s">
-        <v>160</v>
+        <v>97</v>
       </c>
       <c r="B77" t="s">
         <v>8</v>
       </c>
       <c r="C77" t="s">
-        <v>157</v>
+        <v>104</v>
       </c>
       <c r="D77" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E77">
         <v>2.81</v>
@@ -2470,16 +2272,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" t="s">
-        <v>161</v>
+        <v>98</v>
       </c>
       <c r="B78" t="s">
         <v>8</v>
       </c>
       <c r="C78" t="s">
-        <v>162</v>
+        <v>104</v>
       </c>
       <c r="D78" t="s">
-        <v>163</v>
+        <v>99</v>
       </c>
       <c r="E78">
         <v>2.81</v>
@@ -2490,16 +2292,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" t="s">
-        <v>164</v>
+        <v>100</v>
       </c>
       <c r="B79" t="s">
         <v>8</v>
       </c>
       <c r="C79" t="s">
-        <v>159</v>
+        <v>104</v>
       </c>
       <c r="D79" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="E79">
         <v>2.81</v>
@@ -2510,16 +2312,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" t="s">
-        <v>165</v>
+        <v>101</v>
       </c>
       <c r="B80" t="s">
         <v>8</v>
       </c>
       <c r="C80" t="s">
-        <v>166</v>
+        <v>104</v>
       </c>
       <c r="D80" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E80">
         <v>2.82</v>
@@ -2530,16 +2332,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" t="s">
-        <v>167</v>
+        <v>102</v>
       </c>
       <c r="B81" t="s">
         <v>8</v>
       </c>
       <c r="C81" t="s">
-        <v>168</v>
+        <v>104</v>
       </c>
       <c r="D81" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E81">
         <v>2.83</v>
@@ -2550,16 +2352,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" t="s">
-        <v>169</v>
+        <v>103</v>
       </c>
       <c r="B82" t="s">
         <v>8</v>
       </c>
       <c r="C82" t="s">
-        <v>170</v>
+        <v>104</v>
       </c>
       <c r="D82" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="E82">
         <v>2.83</v>
@@ -2738,13 +2540,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7A1B6DF-9F72-4239-BA55-7DCFD5DD4480}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4C9D3E6-251B-438D-BA5F-5EF0F3C617B7}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39E6FF0C-10FB-41A6-A85F-7B5E284D4839}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E56170E-190F-4371-82A1-CDF61D58D398}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33DF9E4F-C13C-416F-8FFF-97C8247FCE00}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6904792A-4E42-45BA-954E-417FF67F1A29}"/>
 </file>